--- a/tests/regression_artifacts/downloads/email_03152025_RECEIPT/current/HAWB9603312.xlsx
+++ b/tests/regression_artifacts/downloads/email_03152025_RECEIPT/current/HAWB9603312.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Invoice Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Invoice Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -772,14 +772,14 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>62046290</t>
+          <t>62034290</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>62046290</t>
+          <t>62034290</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       <c r="AJ2" s="2" t="n"/>
       <c r="AK2" s="2" t="inlineStr">
         <is>
-          <t>62046290</t>
+          <t>62034290</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       <c r="E3" s="4" t="n"/>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>62046290</t>
+          <t>62034290</t>
         </is>
       </c>
       <c r="G3" s="4" t="n"/>
@@ -938,7 +938,7 @@
       <c r="E4" s="4" t="n"/>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>62046290</t>
+          <t>62034290</t>
         </is>
       </c>
       <c r="G4" s="4" t="n"/>
@@ -1012,19 +1012,19 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>HATS AND OTHER HEADGEAR, PLAITED OR MADE BY ASSEMBLING STRIPS</t>
+          <t>Headgear</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>65040000</t>
+          <t>65000090</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65040000</t>
+          <t>65000090</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       <c r="AJ5" s="2" t="n"/>
       <c r="AK5" s="2" t="inlineStr">
         <is>
-          <t>65040000</t>
+          <t>65000090</t>
         </is>
       </c>
     </row>
@@ -1088,7 +1088,7 @@
       <c r="E6" s="4" t="n"/>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>65040000</t>
+          <t>65000090</t>
         </is>
       </c>
       <c r="G6" s="4" t="n"/>
@@ -1155,7 +1155,7 @@
       <c r="E7" s="4" t="n"/>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>65040000</t>
+          <t>65000090</t>
         </is>
       </c>
       <c r="G7" s="4" t="n"/>
@@ -1928,7 +1928,7 @@
       <c r="I27" s="13" t="n"/>
       <c r="J27" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  └ 62046290: 20% CET (53% of value)</t>
+          <t xml:space="preserve">  └ 62034290: 20% CET (53% of value)</t>
         </is>
       </c>
       <c r="K27" s="13" t="n"/>
@@ -1973,7 +1973,7 @@
       <c r="I28" s="13" t="n"/>
       <c r="J28" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  └ 65040000: 20% CET (47% of value)</t>
+          <t xml:space="preserve">  └ 65000090: 20% CET (47% of value)</t>
         </is>
       </c>
       <c r="K28" s="13" t="n"/>
@@ -2505,12 +2505,12 @@
       <c r="D41" s="21" t="n"/>
       <c r="E41" s="21" t="inlineStr">
         <is>
-          <t>HATS AND OTHER HEADGEAR, PLAITED OR MADE BY ASSEMBLING STRIPS</t>
+          <t>Headgear</t>
         </is>
       </c>
       <c r="F41" s="21" t="inlineStr">
         <is>
-          <t>65040000</t>
+          <t>65000090</t>
         </is>
       </c>
       <c r="G41" s="21" t="n"/>
